--- a/docs/exports/club/07780371_AATSL_Emerging_Toastmasters_Club.xlsx
+++ b/docs/exports/club/07780371_AATSL_Emerging_Toastmasters_Club.xlsx
@@ -1,14 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Level Completions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Standing" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Level Completions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="District Rank by Completion " sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Standing" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -566,6 +567,106 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>AATSL Emerging Toastmasters Club</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Club Performance Summary — Division C, Area 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Snapshot as of 2026-06-30  |  District 82 Toastmasters Pathways Dashboard</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>District Rank by Completion Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Level 1 Rank</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Level 2 Rank</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Level 3 Rank</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Level 4+ Rank</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Total Levels Rank</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Out of 164 active clubs district-wide.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/docs/exports/club/07780371_AATSL_Emerging_Toastmasters_Club.xlsx
+++ b/docs/exports/club/07780371_AATSL_Emerging_Toastmasters_Club.xlsx
@@ -501,7 +501,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Snapshot as of 2026-06-30  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 01 Jul 2026, 17:26  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Snapshot as of 2026-06-30  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 01 Jul 2026, 17:26  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -667,14 +667,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -694,7 +693,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Snapshot as of 2026-06-30  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 01 Jul 2026, 17:26  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -708,25 +707,20 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>District Rank</t>
+          <t>Division Rank</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Division Rank</t>
+          <t>Area Rank</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Area Rank</t>
+          <t>Active Members</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Active Members</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>Distinguished Status</t>
         </is>
@@ -734,20 +728,24 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="D7" s="6" t="n">
         <v>26</v>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>District-wide rank by total levels is shown in the table above.</t>
         </is>
       </c>
     </row>

--- a/docs/exports/club/07780371_AATSL_Emerging_Toastmasters_Club.xlsx
+++ b/docs/exports/club/07780371_AATSL_Emerging_Toastmasters_Club.xlsx
@@ -501,7 +501,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 01 Jul 2026, 17:26  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 01 Jul 2026, 17:41  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 01 Jul 2026, 17:26  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 01 Jul 2026, 17:41  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 01 Jul 2026, 17:26  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 01 Jul 2026, 17:41  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>

--- a/docs/exports/club/07780371_AATSL_Emerging_Toastmasters_Club.xlsx
+++ b/docs/exports/club/07780371_AATSL_Emerging_Toastmasters_Club.xlsx
@@ -501,7 +501,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 01 Jul 2026, 17:41  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:25  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 01 Jul 2026, 17:41  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:25  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -634,25 +634,25 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Out of 164 active clubs district-wide.</t>
+          <t>Out of 159 active clubs district-wide.</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 01 Jul 2026, 17:41  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:25  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>

--- a/docs/exports/club/07780371_AATSL_Emerging_Toastmasters_Club.xlsx
+++ b/docs/exports/club/07780371_AATSL_Emerging_Toastmasters_Club.xlsx
@@ -501,7 +501,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:25  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:30  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:25  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:30  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:25  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:30  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>

--- a/docs/exports/club/07780371_AATSL_Emerging_Toastmasters_Club.xlsx
+++ b/docs/exports/club/07780371_AATSL_Emerging_Toastmasters_Club.xlsx
@@ -501,7 +501,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:30  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-05-24  |  Report generated 02 Jul 2026, 16:21  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:30  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-05-24  |  Report generated 02 Jul 2026, 16:21  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -634,19 +634,19 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>36</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9">
@@ -693,7 +693,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:30  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-05-24  |  Report generated 02 Jul 2026, 16:21  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>

--- a/docs/exports/club/07780371_AATSL_Emerging_Toastmasters_Club.xlsx
+++ b/docs/exports/club/07780371_AATSL_Emerging_Toastmasters_Club.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Level Completions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="District Rank by Completion " sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Standing" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Level Completions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="District Rank by Completion " sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Standing" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -501,7 +501,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-05-24  |  Report generated 02 Jul 2026, 16:21  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 02 Jul 2026, 12:25  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-05-24  |  Report generated 02 Jul 2026, 16:21  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 02 Jul 2026, 12:25  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -634,25 +634,25 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Out of 159 active clubs district-wide.</t>
+          <t>Out of 164 active clubs district-wide.</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-05-24  |  Report generated 02 Jul 2026, 16:21  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 02 Jul 2026, 12:25  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>

--- a/docs/exports/club/07780371_AATSL_Emerging_Toastmasters_Club.xlsx
+++ b/docs/exports/club/07780371_AATSL_Emerging_Toastmasters_Club.xlsx
@@ -501,7 +501,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 02 Jul 2026, 12:25  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 02 Jul 2026, 12:37  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 02 Jul 2026, 12:25  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 02 Jul 2026, 12:37  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
         <v>37</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9">
@@ -693,7 +693,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 02 Jul 2026, 12:25  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 02 Jul 2026, 12:37  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>

--- a/docs/exports/club/07780371_AATSL_Emerging_Toastmasters_Club.xlsx
+++ b/docs/exports/club/07780371_AATSL_Emerging_Toastmasters_Club.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Level Completions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="District Rank by Completion " sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Standing" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Level Completions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="District Rank by Completion " sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Standing" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -501,7 +501,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 02 Jul 2026, 12:37  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-05-09  |  Report generated 02 Jul 2026, 18:38  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 02 Jul 2026, 12:37  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-05-09  |  Report generated 02 Jul 2026, 18:38  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -634,25 +634,25 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Out of 164 active clubs district-wide.</t>
+          <t>Out of 158 active clubs district-wide.</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 02 Jul 2026, 12:37  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-05-09  |  Report generated 02 Jul 2026, 18:38  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>

--- a/docs/exports/club/07780371_AATSL_Emerging_Toastmasters_Club.xlsx
+++ b/docs/exports/club/07780371_AATSL_Emerging_Toastmasters_Club.xlsx
@@ -501,7 +501,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-05-09  |  Report generated 02 Jul 2026, 18:38  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 18:44  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-05-09  |  Report generated 02 Jul 2026, 18:38  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 18:44  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -634,13 +634,13 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>36</v>
@@ -652,7 +652,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Out of 158 active clubs district-wide.</t>
+          <t>Out of 159 active clubs district-wide.</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-05-09  |  Report generated 02 Jul 2026, 18:38  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 18:44  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>

--- a/docs/exports/club/07780371_AATSL_Emerging_Toastmasters_Club.xlsx
+++ b/docs/exports/club/07780371_AATSL_Emerging_Toastmasters_Club.xlsx
@@ -501,7 +501,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 18:44  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:51  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -541,19 +541,19 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -594,7 +594,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 18:44  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:51  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -634,25 +634,25 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="B7" s="6" t="n">
         <v>9</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Out of 159 active clubs district-wide.</t>
+          <t>Out of 158 active clubs district-wide.</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 18:44  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:51  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -728,17 +728,17 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B7" s="6" t="n">
         <v>3</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>—</t>
         </is>
       </c>
     </row>

--- a/docs/exports/club/07780371_AATSL_Emerging_Toastmasters_Club.xlsx
+++ b/docs/exports/club/07780371_AATSL_Emerging_Toastmasters_Club.xlsx
@@ -501,7 +501,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:51  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:55  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:51  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:55  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:51  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:55  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>

--- a/docs/exports/club/07780371_AATSL_Emerging_Toastmasters_Club.xlsx
+++ b/docs/exports/club/07780371_AATSL_Emerging_Toastmasters_Club.xlsx
@@ -501,7 +501,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:55  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:02  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:55  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:02  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:55  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:02  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>

--- a/docs/exports/club/07780371_AATSL_Emerging_Toastmasters_Club.xlsx
+++ b/docs/exports/club/07780371_AATSL_Emerging_Toastmasters_Club.xlsx
@@ -501,7 +501,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:02  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:27  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:02  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:27  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:02  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:27  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>

--- a/docs/exports/club/07780371_AATSL_Emerging_Toastmasters_Club.xlsx
+++ b/docs/exports/club/07780371_AATSL_Emerging_Toastmasters_Club.xlsx
@@ -501,7 +501,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:27  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-10-31  |  Report generated 02 Jul 2026, 19:37  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -544,16 +544,16 @@
         <v>1</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -594,7 +594,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:27  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-10-31  |  Report generated 02 Jul 2026, 19:37  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -634,25 +634,25 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Out of 158 active clubs district-wide.</t>
+          <t>Out of 157 active clubs district-wide.</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:27  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-10-31  |  Report generated 02 Jul 2026, 19:37  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B7" s="6" t="n">
         <v>3</v>

--- a/docs/exports/club/07780371_AATSL_Emerging_Toastmasters_Club.xlsx
+++ b/docs/exports/club/07780371_AATSL_Emerging_Toastmasters_Club.xlsx
@@ -501,7 +501,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-10-31  |  Report generated 02 Jul 2026, 19:37  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 19:50  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -541,19 +541,19 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -594,7 +594,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-10-31  |  Report generated 02 Jul 2026, 19:37  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 19:50  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -634,25 +634,25 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Out of 157 active clubs district-wide.</t>
+          <t>Out of 155 active clubs district-wide.</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-10-31  |  Report generated 02 Jul 2026, 19:37  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 19:50  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -734,11 +734,11 @@
         <v>3</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>M</t>
         </is>
       </c>
     </row>

--- a/docs/exports/club/07780371_AATSL_Emerging_Toastmasters_Club.xlsx
+++ b/docs/exports/club/07780371_AATSL_Emerging_Toastmasters_Club.xlsx
@@ -501,7 +501,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 19:50  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 20:06  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 19:50  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 20:06  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 19:50  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 20:06  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>

--- a/docs/exports/club/07780371_AATSL_Emerging_Toastmasters_Club.xlsx
+++ b/docs/exports/club/07780371_AATSL_Emerging_Toastmasters_Club.xlsx
@@ -501,7 +501,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 20:06  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-03-05  |  Report generated 02 Jul 2026, 20:33  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>2</v>
@@ -553,7 +553,7 @@
         <v>2</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -594,7 +594,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 20:06  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-03-05  |  Report generated 02 Jul 2026, 20:33  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -634,25 +634,25 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C7" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="E7" s="6" t="n">
         <v>26</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>36</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>47</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Out of 155 active clubs district-wide.</t>
+          <t>Out of 162 active clubs district-wide.</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 20:06  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-03-05  |  Report generated 02 Jul 2026, 20:33  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -728,17 +728,17 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B7" s="6" t="n">
         <v>3</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>—</t>
         </is>
       </c>
     </row>

--- a/docs/exports/club/07780371_AATSL_Emerging_Toastmasters_Club.xlsx
+++ b/docs/exports/club/07780371_AATSL_Emerging_Toastmasters_Club.xlsx
@@ -501,7 +501,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-03-05  |  Report generated 02 Jul 2026, 20:33  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 04 Jul 2026, 13:03  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>2</v>
@@ -553,7 +553,7 @@
         <v>2</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -594,7 +594,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-03-05  |  Report generated 02 Jul 2026, 20:33  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 04 Jul 2026, 13:03  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -634,25 +634,25 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>26</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Out of 162 active clubs district-wide.</t>
+          <t>Out of 164 active clubs district-wide.</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-03-05  |  Report generated 02 Jul 2026, 20:33  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 04 Jul 2026, 13:03  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -728,17 +728,17 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B7" s="6" t="n">
         <v>3</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>M</t>
         </is>
       </c>
     </row>

--- a/docs/exports/club/07780371_AATSL_Emerging_Toastmasters_Club.xlsx
+++ b/docs/exports/club/07780371_AATSL_Emerging_Toastmasters_Club.xlsx
@@ -501,7 +501,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 04 Jul 2026, 13:03  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 04 Jul 2026, 13:24  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 04 Jul 2026, 13:03  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 04 Jul 2026, 13:24  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 04 Jul 2026, 13:03  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 04 Jul 2026, 13:24  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
